--- a/worklog/v2.2.3/s10/pjm/v3/test/ods_quality_measure_v2.xlsx
+++ b/worklog/v2.2.3/s10/pjm/v3/test/ods_quality_measure_v2.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
   <si>
     <t>项目编号</t>
   </si>
@@ -547,112 +547,130 @@
     <t>仿真初步结果满足要求</t>
   </si>
   <si>
+    <t>PJ-2025-005</t>
+  </si>
+  <si>
+    <t>郭伟</t>
+  </si>
+  <si>
+    <t>PJ-2025-008</t>
+  </si>
+  <si>
+    <t>2025-02-30</t>
+  </si>
+  <si>
+    <t>赵敏</t>
+  </si>
+  <si>
+    <t>PJ-2025-003</t>
+  </si>
+  <si>
     <t>钱海</t>
   </si>
   <si>
-    <t>2025-3-20</t>
-  </si>
-  <si>
-    <t>赵敏</t>
+    <t>PJ-2025-004</t>
+  </si>
+  <si>
+    <t>2025年04月05日</t>
+  </si>
+  <si>
+    <t>秦川</t>
+  </si>
+  <si>
+    <t>20205/05/20</t>
+  </si>
+  <si>
+    <t>王鹏</t>
+  </si>
+  <si>
+    <t>PJ-2025-007</t>
+  </si>
+  <si>
+    <t>待定</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>2025.3.5</t>
   </si>
   <si>
     <t>PJ-2025-006</t>
   </si>
   <si>
-    <t>PJ-2025-005</t>
+    <t>2025-3-18</t>
+  </si>
+  <si>
+    <t>2025.5.10</t>
   </si>
   <si>
     <t>孙伟</t>
   </si>
   <si>
-    <t>2025-3-18</t>
-  </si>
-  <si>
-    <t>2025-03</t>
-  </si>
-  <si>
-    <t>20250/05/15</t>
-  </si>
-  <si>
-    <t>2025年5月20日</t>
-  </si>
-  <si>
-    <t>未知</t>
-  </si>
-  <si>
-    <t>PJ-2025-007</t>
+    <t>2025/03/20</t>
+  </si>
+  <si>
+    <t>2025年3月20日</t>
   </si>
   <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>待定</t>
-  </si>
-  <si>
-    <t>秦川</t>
-  </si>
-  <si>
-    <t>郭伟</t>
-  </si>
-  <si>
     <t>李雪</t>
   </si>
   <si>
-    <t>PJ-2025-003</t>
-  </si>
-  <si>
-    <t>2025/03/18</t>
-  </si>
-  <si>
-    <t>PJ-2025-004</t>
-  </si>
-  <si>
-    <t>王鹏</t>
-  </si>
-  <si>
-    <t>PJ-2025-008</t>
-  </si>
-  <si>
     <t>黄磊</t>
   </si>
   <si>
     <t>2025-04</t>
   </si>
   <si>
-    <t>2025/03/25</t>
-  </si>
-  <si>
-    <t>2025/04/08</t>
-  </si>
-  <si>
-    <t>2025/03/10</t>
-  </si>
-  <si>
-    <t>2025-02-30</t>
-  </si>
-  <si>
-    <t>2025.3.8</t>
-  </si>
-  <si>
-    <t>2025-05</t>
-  </si>
-  <si>
-    <t>20250/04/05</t>
-  </si>
-  <si>
-    <t>2025年04月10日</t>
-  </si>
-  <si>
-    <t>2025/04/02</t>
+    <t>2025-04-32</t>
+  </si>
+  <si>
+    <t>2025/3/10</t>
+  </si>
+  <si>
+    <t>2025/4/5</t>
+  </si>
+  <si>
+    <t>20205/03/18</t>
+  </si>
+  <si>
+    <t>20250/04/25</t>
+  </si>
+  <si>
+    <t>2025-13-05</t>
+  </si>
+  <si>
+    <t>20205/03/08</t>
+  </si>
+  <si>
+    <t>2025-4-1</t>
+  </si>
+  <si>
+    <t>20250/03/20</t>
+  </si>
+  <si>
+    <t>2025-13-20</t>
+  </si>
+  <si>
+    <t>2025年3月10日</t>
+  </si>
+  <si>
+    <t>2025-3-5</t>
+  </si>
+  <si>
+    <t>2025.4.5</t>
+  </si>
+  <si>
+    <t>20205/03/28</t>
+  </si>
+  <si>
+    <t>2025.4.8</t>
   </si>
   <si>
     <t>2025-13-10</t>
-  </si>
-  <si>
-    <t>2025年3月18日</t>
-  </si>
-  <si>
-    <t>2025-03-32</t>
   </si>
 </sst>
 </file>
@@ -1773,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -1791,7 +1809,7 @@
         <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
         <v>40</v>
@@ -1869,12 +1887,12 @@
         <v>57</v>
       </c>
       <c r="AG12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -1892,7 +1910,7 @@
         <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H13" t="s">
         <v>40</v>
@@ -1970,12 +1988,12 @@
         <v>66</v>
       </c>
       <c r="AG13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B14" t="s">
         <v>67</v>
@@ -2071,12 +2089,12 @@
         <v>87</v>
       </c>
       <c r="AG14" t="s">
-        <v>101</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s">
         <v>88</v>
@@ -2172,12 +2190,12 @@
         <v>53</v>
       </c>
       <c r="AG15" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -2240,7 +2258,7 @@
         <v>112</v>
       </c>
       <c r="V16" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="W16" t="s">
         <v>61</v>
@@ -2273,12 +2291,12 @@
         <v>117</v>
       </c>
       <c r="AG16" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -2296,7 +2314,7 @@
         <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="H17" t="s">
         <v>40</v>
@@ -2341,7 +2359,7 @@
         <v>127</v>
       </c>
       <c r="V17" t="s">
-        <v>186</v>
+        <v>39</v>
       </c>
       <c r="W17" t="s">
         <v>40</v>
@@ -2374,12 +2392,12 @@
         <v>131</v>
       </c>
       <c r="AG17" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s">
         <v>67</v>
@@ -2442,7 +2460,7 @@
         <v>143</v>
       </c>
       <c r="V18" t="s">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="W18" t="s">
         <v>145</v>
@@ -2466,7 +2484,7 @@
         <v>146</v>
       </c>
       <c r="AD18" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="AE18" t="s">
         <v>148</v>
@@ -2475,12 +2493,12 @@
         <v>53</v>
       </c>
       <c r="AG18" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>67</v>
@@ -2543,7 +2561,7 @@
         <v>143</v>
       </c>
       <c r="V19" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="W19" t="s">
         <v>145</v>
@@ -2567,7 +2585,7 @@
         <v>53</v>
       </c>
       <c r="AD19" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="AE19" t="s">
         <v>148</v>
@@ -2576,12 +2594,12 @@
         <v>152</v>
       </c>
       <c r="AG19" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s">
         <v>88</v>
@@ -2599,7 +2617,7 @@
         <v>92</v>
       </c>
       <c r="G20" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="H20" t="s">
         <v>61</v>
@@ -2677,12 +2695,12 @@
         <v>163</v>
       </c>
       <c r="AG20" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s">
         <v>164</v>
@@ -2745,7 +2763,7 @@
         <v>125</v>
       </c>
       <c r="V21" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="W21" t="s">
         <v>116</v>
@@ -2879,12 +2897,12 @@
         <v>57</v>
       </c>
       <c r="AG22" t="s">
-        <v>81</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -2902,7 +2920,7 @@
         <v>38</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="H23" t="s">
         <v>40</v>
@@ -2980,12 +2998,12 @@
         <v>66</v>
       </c>
       <c r="AG23" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
         <v>67</v>
@@ -3057,7 +3075,7 @@
         <v>62</v>
       </c>
       <c r="Y24" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="Z24" t="s">
         <v>85</v>
@@ -3072,7 +3090,7 @@
         <v>53</v>
       </c>
       <c r="AD24" t="s">
-        <v>192</v>
+        <v>84</v>
       </c>
       <c r="AE24" t="s">
         <v>85</v>
@@ -3081,12 +3099,12 @@
         <v>87</v>
       </c>
       <c r="AG24" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="B25" t="s">
         <v>88</v>
@@ -3104,7 +3122,7 @@
         <v>92</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>194</v>
       </c>
       <c r="H25" t="s">
         <v>85</v>
@@ -3182,12 +3200,12 @@
         <v>53</v>
       </c>
       <c r="AG25" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -3283,12 +3301,12 @@
         <v>117</v>
       </c>
       <c r="AG26" t="s">
-        <v>195</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -3306,7 +3324,7 @@
         <v>38</v>
       </c>
       <c r="G27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H27" t="s">
         <v>40</v>
@@ -3384,12 +3402,12 @@
         <v>131</v>
       </c>
       <c r="AG27" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
         <v>67</v>
@@ -3407,7 +3425,7 @@
         <v>71</v>
       </c>
       <c r="G28" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="H28" t="s">
         <v>135</v>
@@ -3485,12 +3503,12 @@
         <v>53</v>
       </c>
       <c r="AG28" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s">
         <v>67</v>
@@ -3586,12 +3604,12 @@
         <v>152</v>
       </c>
       <c r="AG29" t="s">
-        <v>201</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s">
         <v>88</v>
@@ -3654,7 +3672,7 @@
         <v>125</v>
       </c>
       <c r="V30" t="s">
-        <v>202</v>
+        <v>63</v>
       </c>
       <c r="W30" t="s">
         <v>56</v>
@@ -3687,12 +3705,12 @@
         <v>163</v>
       </c>
       <c r="AG30" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
         <v>164</v>
@@ -3788,12 +3806,12 @@
         <v>178</v>
       </c>
       <c r="AG31" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
@@ -3856,7 +3874,7 @@
         <v>48</v>
       </c>
       <c r="V32" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="W32" t="s">
         <v>52</v>
@@ -3889,12 +3907,12 @@
         <v>57</v>
       </c>
       <c r="AG32" t="s">
-        <v>184</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
@@ -3912,7 +3930,7 @@
         <v>38</v>
       </c>
       <c r="G33" t="s">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="H33" t="s">
         <v>40</v>
@@ -3981,7 +3999,7 @@
         <v>53</v>
       </c>
       <c r="AD33" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="AE33" t="s">
         <v>56</v>
@@ -3990,12 +4008,12 @@
         <v>66</v>
       </c>
       <c r="AG33" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>195</v>
       </c>
       <c r="B34" t="s">
         <v>67</v>
@@ -4067,7 +4085,7 @@
         <v>62</v>
       </c>
       <c r="Y34" t="s">
-        <v>205</v>
+        <v>84</v>
       </c>
       <c r="Z34" t="s">
         <v>85</v>
@@ -4082,7 +4100,7 @@
         <v>53</v>
       </c>
       <c r="AD34" t="s">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="AE34" t="s">
         <v>85</v>
@@ -4091,12 +4109,12 @@
         <v>87</v>
       </c>
       <c r="AG34" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s">
         <v>88</v>
@@ -4159,7 +4177,7 @@
         <v>48</v>
       </c>
       <c r="V35" t="s">
-        <v>207</v>
+        <v>102</v>
       </c>
       <c r="W35" t="s">
         <v>85</v>
@@ -4183,7 +4201,7 @@
         <v>53</v>
       </c>
       <c r="AD35" t="s">
-        <v>39</v>
+        <v>200</v>
       </c>
       <c r="AE35" t="s">
         <v>40</v>
@@ -4192,12 +4210,12 @@
         <v>53</v>
       </c>
       <c r="AG35" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
@@ -4284,7 +4302,7 @@
         <v>114</v>
       </c>
       <c r="AD36" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="AE36" t="s">
         <v>116</v>
@@ -4293,12 +4311,12 @@
         <v>117</v>
       </c>
       <c r="AG36" t="s">
-        <v>142</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
@@ -4361,7 +4379,7 @@
         <v>127</v>
       </c>
       <c r="V37" t="s">
-        <v>39</v>
+        <v>201</v>
       </c>
       <c r="W37" t="s">
         <v>40</v>
@@ -4394,12 +4412,12 @@
         <v>131</v>
       </c>
       <c r="AG37" t="s">
-        <v>101</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s">
         <v>67</v>
@@ -4495,12 +4513,12 @@
         <v>53</v>
       </c>
       <c r="AG38" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
         <v>67</v>
@@ -4518,7 +4536,7 @@
         <v>71</v>
       </c>
       <c r="G39" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="H39" t="s">
         <v>135</v>
@@ -4596,12 +4614,12 @@
         <v>152</v>
       </c>
       <c r="AG39" t="s">
-        <v>81</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s">
         <v>88</v>
@@ -4619,7 +4637,7 @@
         <v>92</v>
       </c>
       <c r="G40" t="s">
-        <v>209</v>
+        <v>113</v>
       </c>
       <c r="H40" t="s">
         <v>61</v>
@@ -4673,7 +4691,7 @@
         <v>62</v>
       </c>
       <c r="Y40" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="Z40" t="s">
         <v>116</v>
@@ -4688,7 +4706,7 @@
         <v>53</v>
       </c>
       <c r="AD40" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="AE40" t="s">
         <v>116</v>
@@ -4697,12 +4715,12 @@
         <v>163</v>
       </c>
       <c r="AG40" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B41" t="s">
         <v>164</v>
@@ -4798,12 +4816,12 @@
         <v>178</v>
       </c>
       <c r="AG41" t="s">
-        <v>101</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -4899,12 +4917,12 @@
         <v>57</v>
       </c>
       <c r="AG42" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B43" t="s">
         <v>34</v>
@@ -4967,7 +4985,7 @@
         <v>53</v>
       </c>
       <c r="V43" t="s">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="W43" t="s">
         <v>61</v>
@@ -4991,7 +5009,7 @@
         <v>53</v>
       </c>
       <c r="AD43" t="s">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="AE43" t="s">
         <v>56</v>
@@ -5000,12 +5018,12 @@
         <v>66</v>
       </c>
       <c r="AG43" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B44" t="s">
         <v>67</v>
@@ -5092,7 +5110,7 @@
         <v>53</v>
       </c>
       <c r="AD44" t="s">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="AE44" t="s">
         <v>85</v>
@@ -5101,12 +5119,12 @@
         <v>87</v>
       </c>
       <c r="AG44" t="s">
-        <v>101</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="B45" t="s">
         <v>88</v>
@@ -5124,7 +5142,7 @@
         <v>92</v>
       </c>
       <c r="G45" t="s">
-        <v>93</v>
+        <v>192</v>
       </c>
       <c r="H45" t="s">
         <v>85</v>
@@ -5202,12 +5220,12 @@
         <v>53</v>
       </c>
       <c r="AG45" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B46" t="s">
         <v>34</v>
@@ -5270,7 +5288,7 @@
         <v>112</v>
       </c>
       <c r="V46" t="s">
-        <v>113</v>
+        <v>207</v>
       </c>
       <c r="W46" t="s">
         <v>61</v>
@@ -5303,12 +5321,12 @@
         <v>117</v>
       </c>
       <c r="AG46" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="B47" t="s">
         <v>34</v>
@@ -5326,7 +5344,7 @@
         <v>38</v>
       </c>
       <c r="G47" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="H47" t="s">
         <v>40</v>
@@ -5404,12 +5422,12 @@
         <v>131</v>
       </c>
       <c r="AG47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="B48" t="s">
         <v>67</v>
@@ -5505,12 +5523,12 @@
         <v>53</v>
       </c>
       <c r="AG48" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="B49" t="s">
         <v>67</v>
@@ -5606,12 +5624,12 @@
         <v>152</v>
       </c>
       <c r="AG49" t="s">
-        <v>174</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
       <c r="B50" t="s">
         <v>88</v>
@@ -5674,7 +5692,7 @@
         <v>125</v>
       </c>
       <c r="V50" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="W50" t="s">
         <v>56</v>
@@ -5707,12 +5725,12 @@
         <v>163</v>
       </c>
       <c r="AG50" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="B51" t="s">
         <v>164</v>
@@ -5730,7 +5748,7 @@
         <v>168</v>
       </c>
       <c r="G51" t="s">
-        <v>169</v>
+        <v>53</v>
       </c>
       <c r="H51" t="s">
         <v>56</v>
@@ -5775,7 +5793,7 @@
         <v>125</v>
       </c>
       <c r="V51" t="s">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="W51" t="s">
         <v>116</v>
@@ -5799,7 +5817,7 @@
         <v>175</v>
       </c>
       <c r="AD51" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="AE51" t="s">
         <v>177</v>
@@ -5808,12 +5826,12 @@
         <v>178</v>
       </c>
       <c r="AG51" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>196</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
         <v>34</v>
@@ -5900,7 +5918,7 @@
         <v>54</v>
       </c>
       <c r="AD52" t="s">
-        <v>210</v>
+        <v>55</v>
       </c>
       <c r="AE52" t="s">
         <v>56</v>
@@ -5909,12 +5927,12 @@
         <v>57</v>
       </c>
       <c r="AG52" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B53" t="s">
         <v>34</v>
@@ -5977,7 +5995,7 @@
         <v>53</v>
       </c>
       <c r="V53" t="s">
-        <v>211</v>
+        <v>60</v>
       </c>
       <c r="W53" t="s">
         <v>61</v>
@@ -6010,12 +6028,12 @@
         <v>66</v>
       </c>
       <c r="AG53" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B54" t="s">
         <v>67</v>
@@ -6111,12 +6129,12 @@
         <v>87</v>
       </c>
       <c r="AG54" t="s">
-        <v>201</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B55" t="s">
         <v>88</v>
@@ -6134,7 +6152,7 @@
         <v>92</v>
       </c>
       <c r="G55" t="s">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="H55" t="s">
         <v>85</v>
@@ -6179,7 +6197,7 @@
         <v>48</v>
       </c>
       <c r="V55" t="s">
-        <v>102</v>
+        <v>211</v>
       </c>
       <c r="W55" t="s">
         <v>85</v>
@@ -6203,7 +6221,7 @@
         <v>53</v>
       </c>
       <c r="AD55" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="AE55" t="s">
         <v>40</v>
@@ -6212,12 +6230,12 @@
         <v>53</v>
       </c>
       <c r="AG55" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s">
         <v>34</v>
@@ -6235,7 +6253,7 @@
         <v>38</v>
       </c>
       <c r="G56" t="s">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="H56" t="s">
         <v>61</v>
@@ -6313,12 +6331,12 @@
         <v>117</v>
       </c>
       <c r="AG56" t="s">
-        <v>101</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B57" t="s">
         <v>34</v>
@@ -6381,7 +6399,7 @@
         <v>127</v>
       </c>
       <c r="V57" t="s">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="W57" t="s">
         <v>40</v>
@@ -6414,12 +6432,12 @@
         <v>131</v>
       </c>
       <c r="AG57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
@@ -6506,7 +6524,7 @@
         <v>146</v>
       </c>
       <c r="AD58" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AE58" t="s">
         <v>148</v>
@@ -6520,7 +6538,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
@@ -6538,7 +6556,7 @@
         <v>71</v>
       </c>
       <c r="G59" t="s">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="H59" t="s">
         <v>135</v>
@@ -6616,12 +6634,12 @@
         <v>152</v>
       </c>
       <c r="AG59" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="B60" t="s">
         <v>88</v>
@@ -6717,12 +6735,12 @@
         <v>163</v>
       </c>
       <c r="AG60" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="B61" t="s">
         <v>164</v>
@@ -6785,7 +6803,7 @@
         <v>125</v>
       </c>
       <c r="V61" t="s">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="W61" t="s">
         <v>116</v>
@@ -6818,12 +6836,12 @@
         <v>178</v>
       </c>
       <c r="AG61" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
         <v>34</v>
@@ -6841,7 +6859,7 @@
         <v>38</v>
       </c>
       <c r="G62" t="s">
-        <v>39</v>
+        <v>213</v>
       </c>
       <c r="H62" t="s">
         <v>40</v>
@@ -6919,12 +6937,12 @@
         <v>57</v>
       </c>
       <c r="AG62" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B63" t="s">
         <v>34</v>
@@ -6942,7 +6960,7 @@
         <v>38</v>
       </c>
       <c r="G63" t="s">
-        <v>39</v>
+        <v>214</v>
       </c>
       <c r="H63" t="s">
         <v>40</v>
@@ -6987,7 +7005,7 @@
         <v>53</v>
       </c>
       <c r="V63" t="s">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="W63" t="s">
         <v>61</v>
@@ -7020,12 +7038,12 @@
         <v>66</v>
       </c>
       <c r="AG63" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
@@ -7043,7 +7061,7 @@
         <v>71</v>
       </c>
       <c r="G64" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="H64" t="s">
         <v>73</v>
@@ -7097,7 +7115,7 @@
         <v>62</v>
       </c>
       <c r="Y64" t="s">
-        <v>53</v>
+        <v>215</v>
       </c>
       <c r="Z64" t="s">
         <v>85</v>
@@ -7121,12 +7139,12 @@
         <v>87</v>
       </c>
       <c r="AG64" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>196</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
         <v>88</v>
@@ -7144,7 +7162,7 @@
         <v>92</v>
       </c>
       <c r="G65" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="H65" t="s">
         <v>85</v>
@@ -7189,7 +7207,7 @@
         <v>48</v>
       </c>
       <c r="V65" t="s">
-        <v>192</v>
+        <v>102</v>
       </c>
       <c r="W65" t="s">
         <v>85</v>
@@ -7222,12 +7240,12 @@
         <v>53</v>
       </c>
       <c r="AG65" t="s">
-        <v>50</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="B66" t="s">
         <v>34</v>
@@ -7290,7 +7308,7 @@
         <v>112</v>
       </c>
       <c r="V66" t="s">
-        <v>113</v>
+        <v>217</v>
       </c>
       <c r="W66" t="s">
         <v>61</v>
@@ -7323,12 +7341,12 @@
         <v>117</v>
       </c>
       <c r="AG66" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B67" t="s">
         <v>34</v>
@@ -7346,7 +7364,7 @@
         <v>38</v>
       </c>
       <c r="G67" t="s">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="H67" t="s">
         <v>40</v>
@@ -7415,7 +7433,7 @@
         <v>53</v>
       </c>
       <c r="AD67" t="s">
-        <v>128</v>
+        <v>218</v>
       </c>
       <c r="AE67" t="s">
         <v>52</v>
@@ -7424,12 +7442,12 @@
         <v>131</v>
       </c>
       <c r="AG67" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B68" t="s">
         <v>67</v>
@@ -7492,7 +7510,7 @@
         <v>143</v>
       </c>
       <c r="V68" t="s">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="W68" t="s">
         <v>145</v>
@@ -7525,12 +7543,12 @@
         <v>53</v>
       </c>
       <c r="AG68" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="B69" t="s">
         <v>67</v>
@@ -7631,7 +7649,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="B70" t="s">
         <v>88</v>
@@ -7727,12 +7745,12 @@
         <v>163</v>
       </c>
       <c r="AG70" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>182</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
         <v>164</v>
@@ -7795,7 +7813,7 @@
         <v>125</v>
       </c>
       <c r="V71" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="W71" t="s">
         <v>116</v>
@@ -7828,12 +7846,12 @@
         <v>178</v>
       </c>
       <c r="AG71" t="s">
-        <v>50</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>179</v>
       </c>
       <c r="B72" t="s">
         <v>34</v>
@@ -7851,7 +7869,7 @@
         <v>38</v>
       </c>
       <c r="G72" t="s">
-        <v>39</v>
+        <v>201</v>
       </c>
       <c r="H72" t="s">
         <v>40</v>
@@ -7929,12 +7947,12 @@
         <v>57</v>
       </c>
       <c r="AG72" t="s">
-        <v>50</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B73" t="s">
         <v>34</v>
@@ -8021,7 +8039,7 @@
         <v>53</v>
       </c>
       <c r="AD73" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="AE73" t="s">
         <v>56</v>
@@ -8030,12 +8048,12 @@
         <v>66</v>
       </c>
       <c r="AG73" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="B74" t="s">
         <v>67</v>
@@ -8053,7 +8071,7 @@
         <v>71</v>
       </c>
       <c r="G74" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="H74" t="s">
         <v>73</v>
@@ -8107,7 +8125,7 @@
         <v>62</v>
       </c>
       <c r="Y74" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="Z74" t="s">
         <v>85</v>
@@ -8122,7 +8140,7 @@
         <v>53</v>
       </c>
       <c r="AD74" t="s">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="AE74" t="s">
         <v>85</v>
@@ -8131,12 +8149,12 @@
         <v>87</v>
       </c>
       <c r="AG74" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="B75" t="s">
         <v>88</v>
@@ -8154,7 +8172,7 @@
         <v>92</v>
       </c>
       <c r="G75" t="s">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s">
         <v>85</v>
@@ -8232,12 +8250,12 @@
         <v>53</v>
       </c>
       <c r="AG75" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="B76" t="s">
         <v>34</v>
@@ -8333,12 +8351,12 @@
         <v>117</v>
       </c>
       <c r="AG76" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="B77" t="s">
         <v>34</v>
@@ -8434,12 +8452,12 @@
         <v>131</v>
       </c>
       <c r="AG77" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>190</v>
+        <v>118</v>
       </c>
       <c r="B78" t="s">
         <v>67</v>
@@ -8535,12 +8553,12 @@
         <v>53</v>
       </c>
       <c r="AG78" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B79" t="s">
         <v>67</v>
@@ -8636,12 +8654,12 @@
         <v>152</v>
       </c>
       <c r="AG79" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>181</v>
       </c>
       <c r="B80" t="s">
         <v>88</v>
@@ -8737,12 +8755,12 @@
         <v>163</v>
       </c>
       <c r="AG80" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="B81" t="s">
         <v>164</v>
@@ -8838,7 +8856,7 @@
         <v>178</v>
       </c>
       <c r="AG81" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
